--- a/docs/evidence/20261023_利用率服務占比_A段/20261023_利用率服務占比_A段.xlsx
+++ b/docs/evidence/20261023_利用率服務占比_A段/20261023_利用率服務占比_A段.xlsx
@@ -6945,28 +6945,1949 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">2026-02-04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（獨立查核確認頁面日期）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Anthropic spent $4.1B training its models in 2025"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"the $4.5B of revenue involved $2.7B in inference compute expense"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anthropic 2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：研發算力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4.1B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，推論算力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$2.7B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（由毛利 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反推，非直接揭露）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Z.ai 2025H1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">研發 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$183M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／推論 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$9M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MiniMax 2025Q1–Q3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">研發 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$142M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／推論 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$38M</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anthropic Serve = 2.7÷(4.1+2.7) = 0.40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（我算）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Z.ai 0.05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MiniMax 0.21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。中國兩家為第三方算力服務費且營收小，不適用大廠機隊。頁面稱 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anthropic </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">數字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"somewhat speculative"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；頁面「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">54%–62%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」與表內合計不吻合，已註記</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anthropic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Derived]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Information </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">報導＋毛利反推）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Z.ai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MiniMax</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Verified]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IPO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">文件）但口徑為服務費</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anthropic </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">對照）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Information </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">經 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Register</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">secondary </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://www.theregister.com/2025/11/12/openai_spending_report/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025-11-12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Register</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：洩漏之 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">文件顯示 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI 2024 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全年對 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">推論支出 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$3.7B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前三季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$8.7B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；自 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2024 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起付給 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">算力款逾 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$12B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"didn't include details on any training-specific spend" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">發言人稱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"the numbers aren't quite right"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">僅 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Azure</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、僅推論；不含 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CoreWeave</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Google</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非分母完整。注意：搜尋摘要顯示「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$12B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」可能是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2024–2025Q3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">推論／算力款累計，而非訓練支出；現值分母中的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億（訓練）我</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未能找到可證實來源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，疑與此混淆，請 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Project </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端核對現值出處</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Interested-party]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／洩漏文件（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ed Zitron </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">取得），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">否認部分</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Register </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已讀；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zitron </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原文未讀</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">採用（現值出處疑點）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Information </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">經 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">secondary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Reuters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CNBC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；例：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://www.tbsnews.net/node/1367561</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"expenses associated with running its AI models, referred to as inference, increased fourfold in 2025"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">adjusted gross margin 40%→33%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">推論支出 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2024 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍；毛利 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2030 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前總算力支出目標約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$600B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Reuters 2026-02-20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無訓練對推論拆分。可作為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Serve </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趨勢證據：推論支出成長快於總算力的程度未知</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Interested-party]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">對投資人說法）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IPO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前有誘因</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">搜尋摘要所引 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">secondary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">letsdatascience</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">the-decoder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">2026</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（頁面未顯示確切日）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"Anthropic spent $4.1B training its models in 2025"</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Brockman </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法庭證詞 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">算力支出 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$50B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；另有第三方稱 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">訓練 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$32B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、推論 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$14.1B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tracker </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">站，可靠度低）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">若 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$32B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$14.1B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">屬實：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Serve = 14.1÷46.1 = 0.31</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">我多次搜尋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無法證實</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">** $32B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$14.1B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出處（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Information </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原文未取得）。僅供參考、不採用</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／未證實</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">不採用（未證實）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anthropic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Lambda Finance, https://www.lambdafin.com/articles/anthropic-compute-costs </t>
     </r>
     <r>
       <rPr>
@@ -6985,133 +8906,155 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">"the $4.5B of revenue involved $2.7B in inference compute expense"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Anthropic 2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：研發算力 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4.1B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，推論算力 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$2.7B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（由毛利 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">反推，非直接揭露）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Z.ai 2025H1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">研發 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$183M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／推論 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$9M</t>
+      <t xml:space="preserve">2026-06</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述：訓練 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">56%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、推論 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、研究 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Lambda Finance </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">彙整，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SemiAnalysis </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">只是其輸入之一，非公司揭露）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anthropic </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">算力支出占比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">若研究併入研發：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Serve = 33%</t>
     </r>
     <r>
       <rPr>
@@ -7130,76 +9073,193 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MiniMax 2025Q1–Q3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">研發 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$142M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／推論 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$38M</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Anthropic Serve = 2.7÷(4.1+2.7) = 0.40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（我算）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Z.ai 0.05</t>
+      <t xml:space="preserve">SemiAnalysis </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為二手來源，不單獨採信</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Analogy]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／低可信</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不採用（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SemiAnalysis </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">二手）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S9</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Dario Amodei </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">訪談轉述（搜尋摘要）；來源不明</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"roughly half of compute goes to training new models, half to serving inference"——**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">再次搜尋找不到原話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Anthropic ≈ 0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無法驗證，僅列為線索</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Unverified]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Epoch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Erdil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, "Optimally allocating compute between inference and training", https://epoch.ai/blog/optimally-allocating-compute-between-inference-and-training </t>
     </r>
     <r>
       <rPr>
@@ -7218,85 +9278,1564 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MiniMax 0.21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。中國兩家為第三方算力服務費且營收小，不適用大廠機隊。頁面稱 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Anthropic </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">數字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"somewhat speculative"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；頁面「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">54%–62%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」與表內合計不吻合，已註記</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Anthropic</t>
+      <t xml:space="preserve">2024-03-29</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">轉述：成本最小化下訓練與推論支出趨向相等</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">理論：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Serve → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">規範性理論，非實測；可作基準上緣的理論依據</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Analogy]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">參考（理論）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottier et al., Epoch "How much does it cost to train frontier AI models?", https://epoch.ai/publications/how-much-does-it-cost-to-train-frontier-ai-models</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述：總開發成本＝最終訓練 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">實驗／評測／微調倍數，對數常態 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90% CI 1.2×–4×</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">最終訓練占研發算力約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25%–83%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9.6%–23%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）相比倍數偏小，兩者不一致；只說明分母定義的不確定</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">[Derived]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S12</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sarah Friar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部落格，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-01-18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；引 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCD https://datacenterdynamics.com/en/news/openai-cfo-says-company-ended-2025-with-19gw-of-compute-scaled-revenue-at-same-speed/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述：算力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.2 GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.6 GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）→約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.9 GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ARR $2B→$6B→$20B+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">總算力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間序列；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無服務與研發拆分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">可作分母（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">口徑，含訓練與服務）；未說明 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">或設施電力，口徑未明</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">[Interested-party]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">搜尋摘要多處一致，原文 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">403 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未讀</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">參考（分母 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S13</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Brockman</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Friar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">說法（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AOL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">letsdatascience</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">startupfortune </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述：研究團隊與應用團隊之總分配由 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Altman </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Simo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決定；為滿足 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月影像生成需求</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"diverted compute from research"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"very painful"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Friar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：因算力不足婉拒機會</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">無數字</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">質性：服務需求可擠壓研究算力，代表 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Serve </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在短缺期上升</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S14</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DeepSeek </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">服務公開資料（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Atlas Cloud </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025-03</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述：白天全部節點供推論，夜間縮減推論節點改作研究與訓練；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小時內 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">峰值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">278 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節點、平均 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">226.75 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節點（每節點 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">張 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H800</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">服務算力以節點數表示，無總機隊大小</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無分母（訓練 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">數）。僅說明機隊可日夜共用，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以時間平均看；不能換算占比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Verified]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DeepSeek </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自揭）但為二手轉載</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S15</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Alphabet Q1 2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">電話會議（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">fool.com</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vectorshift </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">摘要）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-04-29</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Pichai "compute-constrained in the near term"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ROIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">框架在模型訓練、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">YouTube</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cloud </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">間分配稀缺算力</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">無百分比</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無數字；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Google </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未揭露訓練／推論占比</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S16</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Meta Q4 2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">電話會議；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">itiger </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉載）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zuckerberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">稱 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大部分時間算力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"somewhat constrained"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；廣告推論用較小模型</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S17</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft FY25Q1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">電話會議（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Register 2024-10-31 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉述：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Nadella </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">稱不出租裸 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">供他人訓練，因推論需求高</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">質性：雲端業者偏重推論</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S18</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">repo</t>
     </r>
     <r>
       <rPr>
@@ -7315,7 +10854,395 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">[Derived]</t>
+      <t xml:space="preserve">model/20261023_Tokenomics_v20.1.xlsx SRC_Demand </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SRC_DEM_006</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源欄僅寫 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">openai_token_revenue.json</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（內部檔）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">訓練支出 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$12B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（約值）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">支出口徑，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI 2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.41 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的分母之一；原始外部出處本段查不到（子代理搜尋亦同）。活頁簿 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v17.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已記載「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">組查詢未找到」，非本段新發現</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Interested-party]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，等級 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；出處待補</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">已讀（活頁簿）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S19</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">repo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SRC_Demand </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SRC_DEM_018</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Azure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">帳單，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Where's Your Ed At 2025-11-12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，二手）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">推論 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$12.6B</t>
     </r>
     <r>
       <rPr>
@@ -7334,26 +11261,238 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">The Information </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">報導＋毛利反推）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Z.ai</t>
+      <t xml:space="preserve">12.3–13.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">支出口徑，含 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利潤與資本回收；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q1–Q3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">實際 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">推估</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">若代入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B4_Serve</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12.6/(12.6+12)=0.51</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「約各半」同向。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">雙重計入警告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（獨立查核指出；活頁簿 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SRC_DEM_018 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">備註 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v5.36</t>
     </r>
     <r>
       <rPr>
@@ -7372,26 +11511,45 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MiniMax</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Verified]</t>
+      <t xml:space="preserve">v15.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12.6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$6.55B</t>
     </r>
     <r>
       <rPr>
@@ -7410,167 +11568,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">IPO </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">文件）但口徑為服務費</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">採用（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Anthropic </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">對照）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">The Information </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">經 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Register</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">secondary </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://www.theregister.com/2025/11/12/openai_spending_report/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025-11-12</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Register</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）：洩漏之 </t>
+      <t xml:space="preserve">65.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億美元）未進 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業成本，最可能是研究推論，分子含研究、分母又含訓練；且含 </t>
     </r>
     <r>
       <rPr>
@@ -7589,3824 +11615,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">文件顯示 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI 2024 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">全年對 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">推論支出 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$3.7B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前三季 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$8.7B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；自 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2024 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起付給 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">算力款逾 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$12B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"didn't include details on any training-specific spend" </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">發言人稱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"the numbers aren't quite right"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">僅 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Azure</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、僅推論；不含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CoreWeave</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Google</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非分母完整。注意：搜尋摘要顯示「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$12B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」可能是 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2024–2025Q3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">推論／算力款累計，而非訓練支出；現值分母中的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億（訓練）我</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未能找到可證實來源</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，疑與此混淆，請 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Project </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">端核對現值出處</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Interested-party]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／洩漏文件（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Ed Zitron </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">取得），</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">否認部分</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Register </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已讀；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Zitron </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">原文未讀</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">採用（現值出處疑點）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">The Information </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">經 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">secondary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Reuters</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CNBC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-02</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；例：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://www.tbsnews.net/node/1367561</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"expenses associated with running its AI models, referred to as inference, increased fourfold in 2025"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">adjusted gross margin 40%→33%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">推論支出 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2024 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍；毛利 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">33%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2030 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前總算力支出目標約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$600B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Reuters 2026-02-20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無訓練對推論拆分。可作為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Serve </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趨勢證據：推論支出成長快於總算力的程度未知</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Interested-party]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">對投資人說法）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IPO </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前有誘因</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S7</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">搜尋摘要所引 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">secondary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">letsdatascience</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">the-decoder</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Brockman </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">法庭證詞 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">算力支出 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$50B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；另有第三方稱 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">訓練 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$32B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、推論 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$14.1B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">tracker </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">站，可靠度低）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">若 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$32B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$14.1B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">屬實：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Serve = 14.1÷46.1 = 0.31</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">我多次搜尋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無法證實</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">** $32B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$14.1B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">出處（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">The Information </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">原文未取得）。僅供參考、不採用</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Assumed]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／未證實</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">不採用（未證實）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Anthropic</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Lambda Finance, https://www.lambdafin.com/articles/anthropic-compute-costs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-06</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：訓練 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">56%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、推論 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">33%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、研究 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（引 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SemiAnalysis </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與其他估計，非公司揭露）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Anthropic </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">算力支出占比</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">若研究併入研發：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Serve = 33%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SemiAnalysis </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為二手來源，不單獨採信</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Analogy]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／低可信</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不採用（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SemiAnalysis </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">二手）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S9</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Dario Amodei </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">訪談轉述（搜尋摘要）；來源不明</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"roughly half of compute goes to training new models, half to serving inference"——**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">再次搜尋找不到原話</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">**</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Anthropic ≈ 0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無法驗證，僅列為線索</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Unverified]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S10</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Epoch</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Erdil</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, "Optimally allocating compute between inference and training", https://epoch.ai/blog/optimally-allocating-compute-between-inference-and-training </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2024-03-29</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">轉述：成本最小化下訓練與推論支出趨向相等</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">理論：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Serve → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.5</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">規範性理論，非實測；可作基準上緣的理論依據</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Analogy]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">參考（理論）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cottier et al., Epoch "How much does it cost to train frontier AI models?", https://epoch.ai/publications/how-much-does-it-cost-to-train-frontier-ai-models</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：總開發成本＝最終訓練 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">實驗／評測／微調倍數，對數常態 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">90% CI 1.2×–4×</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">最終訓練占研發算力約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25%–83%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">S2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9.6%–23%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）相比倍數偏小，兩者不一致；只說明分母定義的不確定</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">[Derived]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S12</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sarah Friar </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部落格，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-01-18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；引 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCD https://datacenterdynamics.com/en/news/openai-cfo-says-company-ended-2025-with-19gw-of-compute-scaled-revenue-at-same-speed/</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：算力 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.2 GW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2023</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.6 GW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）→約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.9 GW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ARR $2B→$6B→$20B+</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">總算力 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時間序列；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">**</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無服務與研發拆分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">**</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">可作分母（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">口徑，含訓練與服務）；未說明 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">或設施電力，口徑未明</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">[Interested-party]</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">搜尋摘要多處一致，原文 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">403 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未讀</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">參考（分母 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S13</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Brockman</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Friar </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">說法（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AOL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">letsdatascience</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">startupfortune </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：研究團隊與應用團隊之總分配由 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Altman </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Simo </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">決定；為滿足 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月影像生成需求</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"diverted compute from research"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"very painful"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Friar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：因算力不足婉拒機會</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">無數字</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">質性：服務需求可擠壓研究算力，代表 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Serve </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">在短缺期上升</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S14</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DeepSeek </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">服務公開資料（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Atlas Cloud </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025-03</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：白天全部節點供推論，夜間縮減推論節點改作研究與訓練；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">24 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">小時內 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">V3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">R1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">峰值 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">278 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">節點、平均 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">226.75 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">節點（每節點 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">張 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H800</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">服務算力以節點數表示，無總機隊大小</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無分母（訓練 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GPU </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">數）。僅說明機隊可日夜共用，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以時間平均看；不能換算占比</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Verified]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DeepSeek </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">自揭）但為二手轉載</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Alphabet Q1 2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">電話會議（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">fool.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vectorshift </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">摘要）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-04-29</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Pichai "compute-constrained in the near term"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；以 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ROIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">框架在模型訓練、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Search</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">YouTube</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cloud </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">間分配稀缺算力</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">無百分比</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無數字；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Google </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未揭露訓練／推論占比</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S16</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Meta Q4 2025 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">電話會議；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-01</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">itiger </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉載）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Zuckerberg </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">稱 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">大部分時間算力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"somewhat constrained"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；廣告推論用較小模型</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S17</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft FY25Q1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">電話會議（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">The Register 2024-10-31 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Nadella </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">稱不出租裸 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GPU </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">供他人訓練，因推論需求高</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">質性：雲端業者偏重推論</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S18</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">repo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">model/20261023_Tokenomics_v20.1.xlsx SRC_Demand </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">第 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SRC_DEM_006</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">來源欄僅寫 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">openai_token_revenue.json</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（內部檔）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">訓練支出 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$12B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（約值）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">支出口徑，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI 2025 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年度</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">現值 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.41 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的分母之一；原始外部出處本段查不到（子代理搜尋亦同）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Interested-party]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，等級 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；出處待補</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">已讀（活頁簿）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S19</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">repo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SRC_Demand </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">第 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SRC_DEM_018</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Azure </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">帳單，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Where's Your Ed At 2025-11-12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，二手）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">推論 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$12.6B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12.3–13.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">支出口徑，含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">利潤與資本回收；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Q1–Q3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">實際 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8.67</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Q4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">推估</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">若代入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B4_Serve</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12.6/(12.6+12)=0.51</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">S3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「約各半」同向。與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8.4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">版（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.41</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）並列為口徑差</t>
+      <t xml:space="preserve">加價。故 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.51 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">只作方向，不作範圍上緣的證據</t>
     </r>
   </si>
   <si>
@@ -11857,7 +12085,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；</t>
+      <t xml:space="preserve">（獨立查核無法復現，只找到約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">94%–95%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；</t>
     </r>
     <r>
       <rPr>
@@ -16261,45 +16508,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">證據範圍（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI 2024–2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Anthropic 2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
+      <t xml:space="preserve">證據範圍（扣除 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S19 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後）</t>
     </r>
   </si>
   <si>
@@ -16598,16 +16826,73 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">The Information 2026-02</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），本段與子代理皆未能讀到原文</t>
+      <t xml:space="preserve">The Information</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Why OpenAI, Anthropic Missed Their Own Gross Margin Forecasts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〉約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-02-24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，付費牆），本段與子代理皆未能讀到原文；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段可依此篇名取原文</t>
     </r>
   </si>
   <si>
@@ -21510,7 +21795,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>256</v>
       </c>
@@ -21542,7 +21827,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>264</v>
       </c>
@@ -21620,7 +21905,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
         <v>280</v>
       </c>
@@ -22724,12 +23009,12 @@
         <v>399</v>
       </c>
       <c r="B38" s="12" t="n">
-        <f aca="false">MIN(D32:D36,B37)</f>
+        <f aca="false">MIN(D32:D34,D36,B37)</f>
         <v>0.264705882352941</v>
       </c>
       <c r="C38" s="12" t="n">
-        <f aca="false">MAX(D32:D36,B37)</f>
-        <v>0.51219512195122</v>
+        <f aca="false">MAX(D32:D34,D36,B37)</f>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22796,7 +23081,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
         <v>405</v>
       </c>

--- a/docs/evidence/20261023_利用率服務占比_A段/20261023_利用率服務占比_A段.xlsx
+++ b/docs/evidence/20261023_利用率服務占比_A段/20261023_利用率服務占比_A段.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="488">
   <si>
     <r>
       <rPr>
@@ -3305,7 +3305,1429 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）。原論文 </t>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDF https://ennanzhai.github.io/pub/sosp25-aegaeon.pdf </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">chat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-23 14:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）已讀原文</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Fig.1(a)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">94.1% of 779 models</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.35% of 167.6M requests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17.7% of 30K GPUs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」（長尾＝平均到達率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 1.16 req/s </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的模型）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">§7.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Fig.18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）專屬實例平均 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利用率由「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13.3%∼33.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」提高到「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">48.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,192→213 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">H20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">82%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.8–7B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模型（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TP=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">32–72B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模型（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TP=4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">beta </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逾三個月，「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">no observable SLO violations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SLO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TTFT 10s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TBT 100ms</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長尾專屬實例 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利用率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13.3–33.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小時觀測）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17.7% GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">服務 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.35% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">請求；−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">82% GPU</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">長尾池（約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,300 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）內各模型單一專屬實例的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利用率，觀測 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小時；原文未寫 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Fig.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">觀測期間；無尖峰／平均比；熱門模型利用率原文沒有數字</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">口徑：長尾模型專屬實例，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非機隊平均</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">**</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，且為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利用率（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">活動口徑類），非 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">token </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">產出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷SLO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">產能；只作 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AL_UtilActual </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低端 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的旁證（多模型部署下長尾實例可低到 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.13–0.34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">82% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節省僅對長尾池成立，不可外推</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Interested-party]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Alibaba </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自家系統；共同作者含 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Alibaba </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人員）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">參考（低端 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">旁證）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">U6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://arxiv.org/abs/2407.00079 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mooncake</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Kimi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FAST 2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；已讀 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">arXiv </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">摘要）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">摘要：真實負載下 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Kimi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">多處理 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">請求（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時期；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FAST </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">115%/107%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，僅搜尋摘要）；論文面對「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">highly overloaded scenarios</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」並採預測式提前拒絕</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">無利用率數字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">效能比較，非機隊利用率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">只顯示 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Kimi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在過載下運作（尖峰滿載的旁證），無法換算</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Interested-party]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Moonshot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自家）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">不採用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://arxiv.org/abs/2311.18677 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Splitwise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023-11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；僅讀摘要，</t>
     </r>
     <r>
       <rPr>
@@ -3324,55 +4746,159 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">未取得；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WebFetch </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tom's Hardware </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">頁僅得標題與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,192→213</t>
+      <t xml:space="preserve">為壓縮碼無法解析）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">摘要：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">token generation phase "underutilizes compute resources"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.4× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">吞吐／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-20% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成本</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">單機階段分離</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與機隊時間平均利用率無關；內文是否有 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">diurnal </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">數字未能核實</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Verified] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">學術；本題不可用</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">僅搜尋摘要，未讀原文</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cast AI 2026 State of Kubernetes Optimization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，新聞稿原頁 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://cast.ai/press-release/2026-state-of-kubernetes-optimization-report/ </t>
     </r>
     <r>
       <rPr>
@@ -3391,229 +4917,264 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">17.7%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.35% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">來自 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WebSearch </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">摘要（引述 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Register</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tom's Hardware </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">等）。僅搜尋摘要，未讀原文</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：模型長尾（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt;90% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為低頻模型），專屬實例「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">holding 17.7 percent of GPUs to serve only 1.35 percent</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」的請求</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17.7% GPU </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">服務 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.35% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">請求；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">H20 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">由 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,192 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">降到 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">213</t>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">chat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-23 14:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）已讀原文</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU utilization averaged just 5% across the clusters analyzed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」；「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Average CPU utilization ... 8% in 2025, while memory utilization was 20%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」；樣本寫「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tens of thousands of clusters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">23,000 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">itbrief </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">數字，原頁沒有）；工作負載只寫「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI and ML workloads</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（平均 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利用率）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">企業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Kubernetes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">叢集；指標定義（請求量對使用量、配置量對使用量）原頁未寫；未分推論或訓練</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">口徑差極大，不可換算；維持「不採用」</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Interested-party]</t>
     </r>
     <r>
       <rPr>
@@ -3632,1043 +5193,6 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-82%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">goodput </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">最高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9×</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Model Studio </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的多模型市集；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">beta </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">逾三個月</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">這是「多模型分散部署」的浪費，不是整機隊平均利用率；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">82% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">節省僅對長尾模型池成立，不可外推到全機隊。口徑不同，只作參考</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Interested-party]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Alibaba </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">自家；共同作者含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Alibaba CTO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；誘因：推銷系統</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">僅搜尋摘要，未讀原文</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://arxiv.org/abs/2407.00079 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mooncake</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Kimi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FAST 2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；已讀 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">arXiv </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">摘要）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">摘要：真實負載下 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Kimi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">多處理 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">75% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">請求（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">v1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時期；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FAST </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">版 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">115%/107%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，僅搜尋摘要）；論文面對「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">highly overloaded scenarios</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」並採預測式提前拒絕</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">無利用率數字</t>
-  </si>
-  <si>
-    <t xml:space="preserve">效能比較，非機隊利用率</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">只顯示 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Kimi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">在過載下運作（尖峰滿載的旁證），無法換算</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Interested-party]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Moonshot </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">自家）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">不採用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U7</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://arxiv.org/abs/2311.18677 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Splitwise</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2023-11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；僅讀摘要，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PDF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為壓縮碼無法解析）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">摘要：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">token generation phase "underutilizes compute resources"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.4× </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">吞吐／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-20% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">成本</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">單機階段分離</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與機隊時間平均利用率無關；內文是否有 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">diurnal </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">數字未能核實</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Verified] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">學術；本題不可用</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">U8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cast AI 2026 State of Kubernetes Optimization</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cast.ai</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">itbrief.co.uk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。原頁 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">WebFetch </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">連線失敗（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ENOTFOUND</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；僅搜尋摘要，未讀原文</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轉述：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">23,000 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">個 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">K8s </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">叢集平均 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GPU </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">利用率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CPU 8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、記憶體 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；資料至 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-04</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">5%</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">企業 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Kubernetes </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">叢集，被指派資源 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">實際使用</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">口徑差異極大（含自建、閒置、非推論、請求量 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">使用量）；不可換算，只作參考</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[Interested-party]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">Cast AI </t>
     </r>
     <r>
@@ -4678,7 +5202,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">販售最佳化軟體</t>
+      <t xml:space="preserve">販售最佳化軟體）</t>
     </r>
   </si>
   <si>
@@ -6200,6 +6724,340 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">已讀原文；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">chat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-23 14:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）另已讀 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Epoch CSV https://epoch.ai/data/charts/openai-compute-spend/openai_compute_spend.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025-11-17 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">更新）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R&amp;D Compute Total 50 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPT-4.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">最終訓練估 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4.0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億［</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Actual 3.86 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90% CI 1.7–8.9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億］、其他已發布模型最終訓練 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Other R&amp;D 45 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億＝基礎研究、實驗／去風險 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">run</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、未發布模型），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Inference Compute Total 18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18÷(50+18)=0.265 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與本列一致；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CSV </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">數字</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">採用（</t>
     </r>
     <r>
@@ -15927,6 +16785,101 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段已讀 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Epoch CSV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R&amp;D 50 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億、推論 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18÷68=0.265</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
     </r>
     <r>
       <rPr>
@@ -21013,7 +21966,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>91</v>
       </c>
@@ -21023,13 +21976,13 @@
       <c r="C9" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G9" s="7" t="s">
@@ -21039,10 +21992,10 @@
         <v>97</v>
       </c>
       <c r="I9" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21103,71 +22056,71 @@
         <v>113</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>106</v>
@@ -21175,71 +22128,71 @@
     </row>
     <row r="14" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G14" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>134</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -21251,193 +22204,193 @@
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
     </row>
-    <row r="17" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="364.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>66</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>75</v>
@@ -21445,159 +22398,159 @@
     </row>
     <row r="23" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>66</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>75</v>
@@ -21605,95 +22558,95 @@
     </row>
     <row r="28" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J30" s="7" t="s">
         <v>75</v>
@@ -21701,159 +22654,159 @@
     </row>
     <row r="31" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>247</v>
-      </c>
       <c r="F32" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C35" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>265</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>263</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>75</v>
@@ -21861,7 +22814,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -21875,63 +22828,63 @@
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J38" s="7" t="s">
         <v>75</v>
@@ -21939,31 +22892,31 @@
     </row>
     <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J39" s="7" t="s">
         <v>75</v>
@@ -21971,31 +22924,31 @@
     </row>
     <row r="40" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="E40" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>289</v>
-      </c>
       <c r="F40" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J40" s="7" t="s">
         <v>75</v>
@@ -22003,31 +22956,31 @@
     </row>
     <row r="41" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="H41" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>295</v>
-      </c>
       <c r="I41" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J41" s="7" t="s">
         <v>75</v>
@@ -22035,31 +22988,31 @@
     </row>
     <row r="42" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J42" s="7" t="s">
         <v>75</v>
@@ -22067,31 +23020,31 @@
     </row>
     <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>75</v>
@@ -22099,7 +23052,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
@@ -22113,13 +23066,13 @@
     </row>
     <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
@@ -22127,19 +23080,19 @@
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -22147,19 +23100,19 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
@@ -22167,19 +23120,19 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -22187,19 +23140,19 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
@@ -22207,19 +23160,19 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -22227,19 +23180,19 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
@@ -22247,271 +23200,271 @@
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J64" s="5"/>
     </row>
@@ -22542,12 +23495,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -22560,38 +23513,38 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1.7</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>2.8</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">1/B5</f>
@@ -22600,7 +23553,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B8" s="12" t="n">
         <f aca="false">1/B6</f>
@@ -22609,13 +23562,13 @@
     </row>
     <row r="9" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>0.7</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22632,21 +23585,21 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">$B$7*B9</f>
@@ -22663,7 +23616,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">$B$8*B9</f>
@@ -22680,7 +23633,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B15" s="12" t="n">
         <f aca="false">MIN(B13:D14)</f>
@@ -22697,7 +23650,7 @@
     </row>
     <row r="16" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>0.58</v>
@@ -22706,12 +23659,12 @@
         <v>0.42</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>0.41</v>
@@ -22725,7 +23678,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B18" s="0" t="str">
         <f aca="false">IF(AND(B17&gt;=B15,B17&lt;=D15),"在範圍內","不在")</f>
@@ -22734,7 +23687,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B19" s="11" t="n">
         <v>0.3</v>
@@ -22746,12 +23699,12 @@
         <v>0.65</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -22764,18 +23717,18 @@
         <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B23" s="15" t="n">
         <f aca="false">B19</f>
@@ -22792,7 +23745,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>0.85</v>
@@ -22808,7 +23761,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B25" s="16" t="n">
         <f aca="false">B23*B24</f>
@@ -22825,7 +23778,7 @@
     </row>
     <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B26" s="17" t="n">
         <v>0.465119971743948</v>
@@ -22841,7 +23794,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B27" s="15" t="n">
         <f aca="false">B26/B25</f>
@@ -22858,7 +23811,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B28" s="15" t="n">
         <f aca="false">B27/$C$27</f>
@@ -22873,12 +23826,12 @@
         <v>0.630769230769231</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -22891,21 +23844,21 @@
         <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B32" s="20" t="n">
         <v>5</v>
@@ -22918,12 +23871,12 @@
         <v>0.264705882352941</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B33" s="20" t="n">
         <v>5</v>
@@ -22936,12 +23889,12 @@
         <v>0.285714285714286</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B34" s="20" t="n">
         <v>12</v>
@@ -22954,12 +23907,12 @@
         <v>0.411764705882353</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B35" s="20" t="n">
         <v>12</v>
@@ -22972,12 +23925,12 @@
         <v>0.51219512195122</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B36" s="20" t="n">
         <v>4.1</v>
@@ -22990,23 +23943,23 @@
         <v>0.397058823529412</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B37" s="11" t="n">
         <v>0.5</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B38" s="12" t="n">
         <f aca="false">MIN(D32:D34,D36,B37)</f>
@@ -23019,7 +23972,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>0.3</v>
@@ -23033,19 +23986,19 @@
     </row>
     <row r="40" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B40" s="15" t="n">
         <f aca="false">B37</f>
         <v>0.5</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
@@ -23058,16 +24011,16 @@
         <v>1</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B44" s="21" t="n">
         <v>3.9</v>
@@ -23075,7 +24028,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B45" s="21" t="n">
         <v>8.4</v>
@@ -23083,30 +24036,30 @@
     </row>
     <row r="46" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B46" s="12" t="n">
         <f aca="false">B44/B45</f>
         <v>0.464285714285714</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B47" s="11" t="n">
         <v>0.95</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B48" s="11" t="n">
         <v>0.35</v>
@@ -23120,7 +24073,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B50" s="10"/>
       <c r="C50" s="10"/>
@@ -23133,21 +24086,21 @@
         <v>1</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B52" s="15" t="n">
         <f aca="false">B39</f>
@@ -23164,7 +24117,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B53" s="17" t="n">
         <v>1.12780698259266</v>
@@ -23180,7 +24133,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B54" s="12" t="n">
         <f aca="false">B53*B52</f>
@@ -23197,7 +24150,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B55" s="11" t="n">
         <v>13.07</v>
@@ -23213,7 +24166,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B56" s="22" t="n">
         <f aca="false">B55/B54</f>
@@ -23228,12 +24181,12 @@
         <v>19.3147707626856</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B57" s="17" t="n">
         <v>9.35311859805586</v>
@@ -23249,7 +24202,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B58" s="15" t="n">
         <f aca="false">B56/B57</f>
@@ -23264,12 +24217,12 @@
         <v>2.06506210310434</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B59" s="15" t="n">
         <f aca="false">B58/$C$58</f>
@@ -23289,21 +24242,21 @@
         <v>1</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B62" s="15" t="n">
         <f aca="false">B48</f>
@@ -23320,7 +24273,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B63" s="16" t="n">
         <f aca="false">$C$39*(1-B62)</f>
@@ -23335,12 +24288,12 @@
         <v>0.164</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B64" s="15" t="n">
         <f aca="false">B63/$C$63</f>
@@ -23385,7 +24338,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23393,206 +24346,206 @@
         <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>

--- a/docs/evidence/20261023_利用率服務占比_A段/20261023_利用率服務占比_A段.xlsx
+++ b/docs/evidence/20261023_利用率服務占比_A段/20261023_利用率服務占比_A段.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="495">
   <si>
     <r>
       <rPr>
@@ -12586,6 +12586,110 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">二手轉述 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BigGo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WallStreetCN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FutuBULL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轉載華爾街見聞 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-02-26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），同引 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -12599,7 +12703,102 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（現值來源，使用者提供）</t>
+      <t xml:space="preserve">〈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Why OpenAI, Anthropic Missed Their Own Gross Margin Forecasts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〉；兩份是同一原文的轉述，不互為獨立來源，數字一致（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">84</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">39</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億、毛利 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；原文付費牆未讀</t>
     </r>
   </si>
   <si>
@@ -12719,7 +12918,34 @@
     <t xml:space="preserve">未讀原文</t>
   </si>
   <si>
-    <t xml:space="preserve">採用（唯一直接證據，未獨立驗證）</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">採用（唯一直接證據，未獨立驗證；二手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同源）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">F2</t>
@@ -13786,6 +14012,542 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">／二手</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">F8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">二手轉述 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WallStreetCN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FutuBULL 2026-02-26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">提供 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">docx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">chat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">端已讀全文），引 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Information 2026-02</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI has approximately 910 million weekly active users, of which only about 5% are paying users</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」；免費成本高的原因（質性）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sora </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">影片生成、推理模型比傳統 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LLM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">耗算力；先讓用戶免費體驗高算力功能、後來才加使用限制（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPT-4o </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">吉卜力風格圖片）；定義「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">compute profit margin for paying users (i.e., the revenue share after deducting AI model operating costs)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」；另有隨需加價內容（與本題無關，轉持有成本口徑差那邊）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億週活、約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">付費（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BigGo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">誤作 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9,100 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">萬，以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億為準）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">推論 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">141 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億中付費 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">66%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2030 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">付費 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">94%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">850 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億（同 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BigGo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">數字）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用戶數占比，另有質性成因；不提供 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">token</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／算力占比</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">質性支持 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B4_Free 0.46 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏高的成因（免費層含高算力功能），但不增加數字證據；也補上「付費用戶算力利潤率」的定義</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Interested-party] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">二手轉述</t>
     </r>
   </si>
   <si>
@@ -21773,7 +22535,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -22826,14 +23588,14 @@
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
     </row>
-    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
         <v>273</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="7" t="s">
         <v>275</v>
       </c>
       <c r="D37" s="5" t="s">
@@ -23018,81 +23780,93 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
         <v>308</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="7" t="s">
         <v>309</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="5" t="s">
         <v>311</v>
       </c>
       <c r="F43" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G43" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="H43" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="I43" s="5" t="s">
         <v>314</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>265</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
+    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
+      <c r="B44" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="J46" s="5"/>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
     </row>
-    <row r="47" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -23100,19 +23874,19 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J47" s="5"/>
     </row>
-    <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
@@ -23120,19 +23894,19 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J48" s="5"/>
     </row>
-    <row r="49" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -23140,19 +23914,19 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
@@ -23160,19 +23934,19 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J50" s="5"/>
     </row>
-    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -23180,19 +23954,19 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
@@ -23200,273 +23974,293 @@
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>327</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>329</v>
+        <v>333</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>334</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>331</v>
+        <v>335</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>336</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="J64" s="5"/>
+    </row>
+    <row r="65" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="J65" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -23495,12 +24289,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -23513,38 +24307,38 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1.7</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>2.8</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B7" s="12" t="n">
         <f aca="false">1/B5</f>
@@ -23553,7 +24347,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B8" s="12" t="n">
         <f aca="false">1/B6</f>
@@ -23562,13 +24356,13 @@
     </row>
     <row r="9" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>0.7</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23585,21 +24379,21 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">$B$7*B9</f>
@@ -23616,7 +24410,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">$B$8*B9</f>
@@ -23633,7 +24427,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B15" s="12" t="n">
         <f aca="false">MIN(B13:D14)</f>
@@ -23650,7 +24444,7 @@
     </row>
     <row r="16" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>0.58</v>
@@ -23659,12 +24453,12 @@
         <v>0.42</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>0.41</v>
@@ -23678,7 +24472,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B18" s="0" t="str">
         <f aca="false">IF(AND(B17&gt;=B15,B17&lt;=D15),"在範圍內","不在")</f>
@@ -23687,7 +24481,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B19" s="11" t="n">
         <v>0.3</v>
@@ -23699,12 +24493,12 @@
         <v>0.65</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -23717,18 +24511,18 @@
         <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B23" s="15" t="n">
         <f aca="false">B19</f>
@@ -23745,7 +24539,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>0.85</v>
@@ -23761,7 +24555,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B25" s="16" t="n">
         <f aca="false">B23*B24</f>
@@ -23778,7 +24572,7 @@
     </row>
     <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B26" s="17" t="n">
         <v>0.465119971743948</v>
@@ -23794,7 +24588,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B27" s="15" t="n">
         <f aca="false">B26/B25</f>
@@ -23811,7 +24605,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B28" s="15" t="n">
         <f aca="false">B27/$C$27</f>
@@ -23826,12 +24620,12 @@
         <v>0.630769230769231</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -23844,21 +24638,21 @@
         <v>1</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B32" s="20" t="n">
         <v>5</v>
@@ -23871,12 +24665,12 @@
         <v>0.264705882352941</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B33" s="20" t="n">
         <v>5</v>
@@ -23889,12 +24683,12 @@
         <v>0.285714285714286</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="B34" s="20" t="n">
         <v>12</v>
@@ -23907,12 +24701,12 @@
         <v>0.411764705882353</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B35" s="20" t="n">
         <v>12</v>
@@ -23925,12 +24719,12 @@
         <v>0.51219512195122</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B36" s="20" t="n">
         <v>4.1</v>
@@ -23943,23 +24737,23 @@
         <v>0.397058823529412</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="B37" s="11" t="n">
         <v>0.5</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B38" s="12" t="n">
         <f aca="false">MIN(D32:D34,D36,B37)</f>
@@ -23972,7 +24766,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>0.3</v>
@@ -23986,19 +24780,19 @@
     </row>
     <row r="40" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B40" s="15" t="n">
         <f aca="false">B37</f>
         <v>0.5</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
@@ -24011,16 +24805,16 @@
         <v>1</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B44" s="21" t="n">
         <v>3.9</v>
@@ -24028,7 +24822,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B45" s="21" t="n">
         <v>8.4</v>
@@ -24036,30 +24830,30 @@
     </row>
     <row r="46" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B46" s="12" t="n">
         <f aca="false">B44/B45</f>
         <v>0.464285714285714</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="B47" s="11" t="n">
         <v>0.95</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B48" s="11" t="n">
         <v>0.35</v>
@@ -24073,7 +24867,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B50" s="10"/>
       <c r="C50" s="10"/>
@@ -24086,16 +24880,16 @@
         <v>1</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24117,7 +24911,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B53" s="17" t="n">
         <v>1.12780698259266</v>
@@ -24133,7 +24927,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B54" s="12" t="n">
         <f aca="false">B53*B52</f>
@@ -24150,7 +24944,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B55" s="11" t="n">
         <v>13.07</v>
@@ -24166,7 +24960,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B56" s="22" t="n">
         <f aca="false">B55/B54</f>
@@ -24181,12 +24975,12 @@
         <v>19.3147707626856</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="B57" s="17" t="n">
         <v>9.35311859805586</v>
@@ -24202,7 +24996,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B58" s="15" t="n">
         <f aca="false">B56/B57</f>
@@ -24217,12 +25011,12 @@
         <v>2.06506210310434</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B59" s="15" t="n">
         <f aca="false">B58/$C$58</f>
@@ -24242,16 +25036,16 @@
         <v>1</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24273,7 +25067,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B63" s="16" t="n">
         <f aca="false">$C$39*(1-B62)</f>
@@ -24288,12 +25082,12 @@
         <v>0.164</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B64" s="15" t="n">
         <f aca="false">B63/$C$63</f>
@@ -24338,7 +25132,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24346,206 +25140,206 @@
         <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>139</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
